--- a/data/Penalty_tracker.xlsx
+++ b/data/Penalty_tracker.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.77734375" customWidth="1" min="3" max="3"/>
@@ -2933,6 +2933,702 @@
         <v>45964</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>5</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F104" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>6</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F105" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>6</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1013</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F106" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>11</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1023</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F107" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>13</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>1023</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F108" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>12</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>16</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F109" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>14</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>17</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F110" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>11</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1920</v>
+      </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F111" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>11</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>26</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F112" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>14</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>26</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F113" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>11</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>487</v>
+      </c>
+      <c r="D114" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F114" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>8</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>87</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F115" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>2</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>913</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F116" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>2</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>1013</v>
+      </c>
+      <c r="D117" t="n">
+        <v>2</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F117" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>2</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>1013</v>
+      </c>
+      <c r="D118" t="n">
+        <v>2</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F118" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>7</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>1013</v>
+      </c>
+      <c r="D119" t="n">
+        <v>2</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F119" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>11</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>1023</v>
+      </c>
+      <c r="D120" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F120" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>7</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>1308</v>
+      </c>
+      <c r="D121" t="n">
+        <v>2</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F121" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>13</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>16</v>
+      </c>
+      <c r="D122" t="n">
+        <v>2</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F122" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>13</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>16</v>
+      </c>
+      <c r="D123" t="n">
+        <v>2</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F123" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>14</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>16</v>
+      </c>
+      <c r="D124" t="n">
+        <v>2</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F124" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>6</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>17</v>
+      </c>
+      <c r="D125" t="n">
+        <v>2</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F125" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>8</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>17</v>
+      </c>
+      <c r="D126" t="n">
+        <v>2</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F126" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>14</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>17</v>
+      </c>
+      <c r="D127" t="n">
+        <v>2</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F127" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>6</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1920</v>
+      </c>
+      <c r="D128" t="n">
+        <v>2</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F128" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>1</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>487</v>
+      </c>
+      <c r="D129" t="n">
+        <v>2</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F129" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>7</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>87</v>
+      </c>
+      <c r="D130" t="n">
+        <v>2</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F130" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>7</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>87</v>
+      </c>
+      <c r="D131" t="n">
+        <v>2</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F131" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>6</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>913</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Rock and Roller Queens</t>
+        </is>
+      </c>
+      <c r="F132" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
